--- a/data/trans_orig/P1411-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2012</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10176</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279858</t>
+          <t>279129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291883</t>
+          <t>291871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277069</t>
+          <t>276197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286185</t>
+          <t>286152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561763</t>
+          <t>560750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575884</t>
+          <t>576060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490900</t>
+          <t>491805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502458</t>
+          <t>502403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510415</t>
+          <t>512005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521662</t>
+          <t>521691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1008124</t>
+          <t>1007999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022115</t>
+          <t>1022070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312868</t>
+          <t>312949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322053</t>
+          <t>322060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333812</t>
+          <t>333575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650734</t>
+          <t>650604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662030</t>
+          <t>662003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23824</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>12858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32317</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350158</t>
+          <t>349486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366319</t>
+          <t>366337</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>374950</t>
+          <t>375747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>385838</t>
+          <t>386022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731350</t>
+          <t>730616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750305</t>
+          <t>750075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21566</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195997</t>
+          <t>195906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208398</t>
+          <t>208255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>209910</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218573</t>
+          <t>218590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410643</t>
+          <t>410534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425797</t>
+          <t>424738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261525</t>
+          <t>261428</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271849</t>
+          <t>271882</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271220</t>
+          <t>272597</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548916</t>
+          <t>548928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19250</t>
+          <t>19528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643538</t>
+          <t>643260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>656908</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682139</t>
+          <t>682087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691841</t>
+          <t>691858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330050</t>
+          <t>1330472</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346425</t>
+          <t>1347100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>22081</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>758181</t>
+          <t>757017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773618</t>
+          <t>773658</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805101</t>
+          <t>805115</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817118</t>
+          <t>817258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568752</t>
+          <t>1568866</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588458</t>
+          <t>1588561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>54956</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>92074</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51613</t>
+          <t>52273</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88276</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132212</t>
+          <t>132501</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3334078</t>
+          <t>3334705</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371246</t>
+          <t>3371823</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3502303</t>
+          <t>3501643</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3527271</t>
+          <t>3526754</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6848482</t>
+          <t>6848193</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6890882</t>
+          <t>6892418</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de infarto de miocardio en 2016</t>
+          <t>Población con diagnóstico de infarto de miocardio en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282687</t>
+          <t>282807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291993</t>
+          <t>292007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277113</t>
+          <t>277079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287490</t>
+          <t>287517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564987</t>
+          <t>565826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578065</t>
+          <t>578162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21958</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>31286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480617</t>
+          <t>481463</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495709</t>
+          <t>496570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508287</t>
+          <t>507169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519657</t>
+          <t>519651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>993795</t>
+          <t>994373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012870</t>
+          <t>1012948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308702</t>
+          <t>308197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316861</t>
+          <t>316356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331745</t>
+          <t>331751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643086</t>
+          <t>643610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652430</t>
+          <t>652266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14663</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356899</t>
+          <t>357498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367290</t>
+          <t>367194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382443</t>
+          <t>381251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742584</t>
+          <t>743321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753606</t>
+          <t>753740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202355</t>
+          <t>201359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210169</t>
+          <t>210182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204753</t>
+          <t>203533</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216174</t>
+          <t>215272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410487</t>
+          <t>410714</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424045</t>
+          <t>424591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251580</t>
+          <t>250985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261154</t>
+          <t>261064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256284</t>
+          <t>256525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269019</t>
+          <t>268919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512480</t>
+          <t>512981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528070</t>
+          <t>527878</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18773</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>637785</t>
+          <t>638195</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651441</t>
+          <t>652060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680377</t>
+          <t>679130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>690043</t>
+          <t>690039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322485</t>
+          <t>1323490</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1339757</t>
+          <t>1340087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41101</t>
+          <t>42698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>749025</t>
+          <t>748155</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767174</t>
+          <t>767109</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>807648</t>
+          <t>806288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821665</t>
+          <t>821871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1563649</t>
+          <t>1562052</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1585868</t>
+          <t>1586257</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51860</t>
+          <t>52334</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85225</t>
+          <t>84642</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>32596</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60519</t>
+          <t>60112</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92504</t>
+          <t>92978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136450</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3309125</t>
+          <t>3309708</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342490</t>
+          <t>3342016</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3484023</t>
+          <t>3484430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511710</t>
+          <t>3511946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6802442</t>
+          <t>6804640</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6846388</t>
+          <t>6845914</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1411-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1411-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21233</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>279129</t>
+          <t>280274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291871</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276197</t>
+          <t>276435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286152</t>
+          <t>286173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560750</t>
+          <t>562193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576060</t>
+          <t>576714</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491805</t>
+          <t>490765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502403</t>
+          <t>502377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512005</t>
+          <t>511807</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521691</t>
+          <t>521806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007999</t>
+          <t>1008166</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022070</t>
+          <t>1022918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>312949</t>
+          <t>312473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>322060</t>
+          <t>322038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333575</t>
+          <t>334084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650604</t>
+          <t>650287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>662003</t>
+          <t>661972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>23929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32317</t>
+          <t>32501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349486</t>
+          <t>350053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366337</t>
+          <t>366317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375747</t>
+          <t>375192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386022</t>
+          <t>385992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730616</t>
+          <t>730432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>750075</t>
+          <t>750192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195906</t>
+          <t>196126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208255</t>
+          <t>208357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209910</t>
+          <t>208979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218590</t>
+          <t>218587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410534</t>
+          <t>410992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424738</t>
+          <t>425770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261428</t>
+          <t>261475</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271882</t>
+          <t>271007</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272597</t>
+          <t>272654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537534</t>
+          <t>537474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548928</t>
+          <t>548904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>643260</t>
+          <t>643396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656908</t>
+          <t>656765</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682087</t>
+          <t>682065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>691858</t>
+          <t>691823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1330472</t>
+          <t>1330214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1347100</t>
+          <t>1347104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757017</t>
+          <t>756743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773658</t>
+          <t>773606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>805115</t>
+          <t>804469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817258</t>
+          <t>817142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568866</t>
+          <t>1569092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1588561</t>
+          <t>1588707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>55594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>26921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52273</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88276</t>
+          <t>87559</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132501</t>
+          <t>131258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3334705</t>
+          <t>3335590</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3371823</t>
+          <t>3371185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3501643</t>
+          <t>3502501</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3526754</t>
+          <t>3526995</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6848193</t>
+          <t>6849436</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6892418</t>
+          <t>6893135</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282807</t>
+          <t>282979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292007</t>
+          <t>291991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277079</t>
+          <t>278159</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287517</t>
+          <t>287605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565826</t>
+          <t>565651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578162</t>
+          <t>578021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31566</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481463</t>
+          <t>481627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496570</t>
+          <t>496031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507169</t>
+          <t>506946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519651</t>
+          <t>519643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>994373</t>
+          <t>994093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012948</t>
+          <t>1013732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308197</t>
+          <t>307888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316356</t>
+          <t>316682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331751</t>
+          <t>331526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643610</t>
+          <t>643608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652266</t>
+          <t>652397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357498</t>
+          <t>357344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367194</t>
+          <t>367221</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381251</t>
+          <t>382347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743321</t>
+          <t>743598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753740</t>
+          <t>754352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201359</t>
+          <t>202125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210182</t>
+          <t>210175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203533</t>
+          <t>203278</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215272</t>
+          <t>216200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410714</t>
+          <t>411645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424591</t>
+          <t>424466</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16590</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>23546</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250985</t>
+          <t>250744</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261064</t>
+          <t>261098</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256525</t>
+          <t>256163</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>268919</t>
+          <t>268863</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>512981</t>
+          <t>512692</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527878</t>
+          <t>528053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,39 +6127,39 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11357</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4767</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>12164</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>638195</t>
+          <t>637029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>652060</t>
+          <t>651699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,42 +6240,42 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>686527</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>679937</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>690081</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>686527</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>679130</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>690039</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1323490</t>
+          <t>1323416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340087</t>
+          <t>1340016</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30428</t>
+          <t>29735</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42698</t>
+          <t>40679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>748155</t>
+          <t>748848</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>767109</t>
+          <t>767155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>806288</t>
+          <t>808862</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>821871</t>
+          <t>821712</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1562052</t>
+          <t>1564071</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1586257</t>
+          <t>1586280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52334</t>
+          <t>51236</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84642</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32596</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60112</t>
+          <t>60992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92978</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134252</t>
+          <t>133851</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3309708</t>
+          <t>3309565</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3342016</t>
+          <t>3343114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3483550</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3511946</t>
+          <t>3511959</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6804640</t>
+          <t>6805041</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6845914</t>
+          <t>6848174</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
